--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193281</v>
+        <v>125193570</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488990</v>
+        <v>489014</v>
       </c>
       <c r="R2" t="n">
-        <v>6890078</v>
+        <v>6890051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193624</v>
+        <v>125193281</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489045</v>
+        <v>488990</v>
       </c>
       <c r="R3" t="n">
-        <v>6890036</v>
+        <v>6890078</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193570</v>
+        <v>125193624</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489014</v>
+        <v>489045</v>
       </c>
       <c r="R4" t="n">
-        <v>6890051</v>
+        <v>6890036</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193570</v>
+        <v>125193281</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489014</v>
+        <v>488990</v>
       </c>
       <c r="R2" t="n">
-        <v>6890051</v>
+        <v>6890078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193281</v>
+        <v>125193831</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,17 +810,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488990</v>
+        <v>488997</v>
       </c>
       <c r="R3" t="n">
-        <v>6890078</v>
+        <v>6890005</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193831</v>
+        <v>125193570</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488997</v>
+        <v>489014</v>
       </c>
       <c r="R5" t="n">
-        <v>6890005</v>
+        <v>6890051</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193281</v>
+        <v>125193570</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488990</v>
+        <v>489014</v>
       </c>
       <c r="R2" t="n">
-        <v>6890078</v>
+        <v>6890051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193831</v>
+        <v>125193281</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -810,26 +810,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488997</v>
+        <v>488990</v>
       </c>
       <c r="R3" t="n">
-        <v>6890005</v>
+        <v>6890078</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193624</v>
+        <v>125193831</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,20 +912,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489045</v>
+        <v>488997</v>
       </c>
       <c r="R4" t="n">
-        <v>6890036</v>
+        <v>6890005</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193570</v>
+        <v>125193624</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489014</v>
+        <v>489045</v>
       </c>
       <c r="R5" t="n">
-        <v>6890051</v>
+        <v>6890036</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193570</v>
+        <v>125193281</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489014</v>
+        <v>488990</v>
       </c>
       <c r="R2" t="n">
-        <v>6890051</v>
+        <v>6890078</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193281</v>
+        <v>125193570</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488990</v>
+        <v>489014</v>
       </c>
       <c r="R3" t="n">
-        <v>6890078</v>
+        <v>6890051</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193831</v>
+        <v>125193624</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -912,29 +912,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488997</v>
+        <v>489045</v>
       </c>
       <c r="R4" t="n">
-        <v>6890005</v>
+        <v>6890036</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193624</v>
+        <v>125193831</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,20 +1014,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489045</v>
+        <v>488997</v>
       </c>
       <c r="R5" t="n">
-        <v>6890036</v>
+        <v>6890005</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193281</v>
+        <v>125193624</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488990</v>
+        <v>489045</v>
       </c>
       <c r="R2" t="n">
-        <v>6890078</v>
+        <v>6890036</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125193570</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193624</v>
+        <v>125193831</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,20 +912,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489045</v>
+        <v>488997</v>
       </c>
       <c r="R4" t="n">
-        <v>6890036</v>
+        <v>6890005</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193831</v>
+        <v>125193281</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,26 +1023,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488997</v>
+        <v>488990</v>
       </c>
       <c r="R5" t="n">
-        <v>6890005</v>
+        <v>6890078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193624</v>
+        <v>125193281</v>
       </c>
       <c r="B2" t="n">
         <v>98269</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489045</v>
+        <v>488990</v>
       </c>
       <c r="R2" t="n">
-        <v>6890036</v>
+        <v>6890078</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193570</v>
+        <v>125193624</v>
       </c>
       <c r="B3" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489014</v>
+        <v>489045</v>
       </c>
       <c r="R3" t="n">
-        <v>6890051</v>
+        <v>6890036</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193831</v>
+        <v>125193570</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>78684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488997</v>
+        <v>489014</v>
       </c>
       <c r="R4" t="n">
-        <v>6890005</v>
+        <v>6890051</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193281</v>
+        <v>125193831</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1023,17 +1014,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488990</v>
+        <v>488997</v>
       </c>
       <c r="R5" t="n">
-        <v>6890078</v>
+        <v>6890005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193281</v>
+        <v>125193570</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488990</v>
+        <v>489014</v>
       </c>
       <c r="R2" t="n">
-        <v>6890078</v>
+        <v>6890051</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,12 +775,7 @@
         <v>125193624</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,50 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193570</v>
+        <v>125193281</v>
       </c>
       <c r="B4" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489014</v>
+        <v>488990</v>
       </c>
       <c r="R4" t="n">
-        <v>6890051</v>
+        <v>6890078</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +969,7 @@
         <v>125193831</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125193624</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125193281</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125193831</v>
       </c>
       <c r="B5" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193281</v>
+        <v>125193831</v>
       </c>
       <c r="B4" t="n">
         <v>98331</v>
@@ -897,17 +897,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488990</v>
+        <v>488997</v>
       </c>
       <c r="R4" t="n">
-        <v>6890078</v>
+        <v>6890005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +975,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193831</v>
+        <v>125193281</v>
       </c>
       <c r="B5" t="n">
         <v>98331</v>
@@ -994,26 +1003,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488997</v>
+        <v>488990</v>
       </c>
       <c r="R5" t="n">
-        <v>6890005</v>
+        <v>6890078</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193570</v>
+        <v>125193238</v>
       </c>
       <c r="B2" t="n">
-        <v>78726</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489014</v>
+        <v>488985</v>
       </c>
       <c r="R2" t="n">
-        <v>6890051</v>
+        <v>6890090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193624</v>
+        <v>125193281</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+          <t>Råbäcken, Råbäcken, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489045</v>
+        <v>488990</v>
       </c>
       <c r="R3" t="n">
-        <v>6890036</v>
+        <v>6890078</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193831</v>
+        <v>125193624</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -897,29 +897,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488997</v>
+        <v>489045</v>
       </c>
       <c r="R4" t="n">
-        <v>6890005</v>
+        <v>6890036</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193281</v>
+        <v>125193831</v>
       </c>
       <c r="B5" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,17 +994,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råbäcken, Råbäcken, Hls</t>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488990</v>
+        <v>488997</v>
       </c>
       <c r="R5" t="n">
-        <v>6890078</v>
+        <v>6890005</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1069,200 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125193570</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-Gumjansgraven, Lill-Gumjansgraven, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>489014</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6890051</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125193330</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råbäcken, Råbäcken, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488963</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6890077</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17368-2023 artfynd.xlsx
+++ b/artfynd/A 17368-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193238</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193624</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193831</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193570</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,8 +1293,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>